--- a/#LALIGA_anonymized.xlsx
+++ b/#LALIGA_anonymized.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -613,7 +613,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -10734,7 +10734,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K313" t="inlineStr"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K334" t="inlineStr"/>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K355" t="inlineStr"/>
@@ -13465,7 +13465,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K370" t="inlineStr"/>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K391" t="inlineStr"/>
@@ -14801,7 +14801,7 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K408" t="inlineStr"/>
@@ -14846,7 +14846,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K409" t="inlineStr"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K430" t="inlineStr"/>
@@ -16292,7 +16292,7 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K451" t="inlineStr"/>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K472" t="inlineStr"/>
@@ -17748,7 +17748,7 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K493" t="inlineStr"/>
@@ -18597,7 +18597,7 @@
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K515" t="inlineStr"/>
@@ -19309,7 +19309,7 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K536" t="inlineStr"/>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K553" t="inlineStr"/>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K574" t="inlineStr"/>
@@ -21327,7 +21327,7 @@
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K595" t="inlineStr"/>
@@ -22071,7 +22071,7 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K616" t="inlineStr"/>
@@ -22818,7 +22818,7 @@
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K637" t="inlineStr"/>
@@ -23573,7 +23573,7 @@
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K658" t="inlineStr"/>
@@ -23613,7 +23613,7 @@
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K659" t="inlineStr"/>
@@ -24336,7 +24336,7 @@
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K680" t="inlineStr"/>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K700" t="inlineStr"/>
@@ -25701,7 +25701,7 @@
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K720" t="inlineStr"/>
@@ -26449,7 +26449,7 @@
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K741" t="inlineStr"/>
@@ -27205,7 +27205,7 @@
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K762" t="inlineStr"/>
@@ -27889,7 +27889,7 @@
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K782" t="inlineStr"/>
@@ -28558,7 +28558,7 @@
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K801" t="inlineStr"/>
@@ -29310,7 +29310,7 @@
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K822" t="inlineStr"/>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K844" t="inlineStr"/>
@@ -30752,7 +30752,7 @@
       </c>
       <c r="J863" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K863" t="inlineStr"/>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="J881" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K881" t="inlineStr"/>
@@ -32128,7 +32128,7 @@
       </c>
       <c r="J902" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K902" t="inlineStr"/>
@@ -32906,7 +32906,7 @@
       </c>
       <c r="J923" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K923" t="inlineStr"/>
@@ -33653,7 +33653,7 @@
       </c>
       <c r="J944" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K944" t="inlineStr"/>
@@ -34390,7 +34390,7 @@
       </c>
       <c r="J965" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K965" t="inlineStr"/>
@@ -35127,7 +35127,7 @@
       </c>
       <c r="J986" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K986" t="inlineStr"/>
@@ -35880,7 +35880,7 @@
       </c>
       <c r="J1007" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K1007" t="inlineStr"/>
@@ -36627,7 +36627,7 @@
       </c>
       <c r="J1028" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K1028" t="inlineStr"/>
@@ -37370,7 +37370,7 @@
       </c>
       <c r="J1049" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K1049" t="inlineStr"/>
@@ -38079,7 +38079,7 @@
       </c>
       <c r="J1070" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K1070" t="inlineStr"/>
